--- a/output/pdf_financials_xlsx/GTCH.xlsx
+++ b/output/pdf_financials_xlsx/GTCH.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.161316</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.591046</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.783033</v>
       </c>
     </row>
     <row r="93">
@@ -3175,7 +3175,11 @@
           <t>SHARE-BASED PAYMENT RESERVE (Note 8)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3204,7 +3208,11 @@
           <t>WARRANTS RESERVE (Note 8)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -3489,7 +3497,11 @@
           <t>WARRANTS RESERVE (Note 8)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>0.161316</v>
       </c>

--- a/output/pdf_financials_xlsx/GTCH.xlsx
+++ b/output/pdf_financials_xlsx/GTCH.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.040133</v>
       </c>
     </row>
     <row r="13">
@@ -867,7 +867,7 @@
         <v>-6.007177</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.126958</v>
+        <v>-3.167091</v>
       </c>
     </row>
     <row r="28">
@@ -899,7 +899,7 @@
         <v>-5.993502</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.102874</v>
+        <v>-3.143007</v>
       </c>
     </row>
     <row r="30">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.316078</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>1.787302</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.316078</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>1.787302</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.466288</v>
+        <v>0.15021</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.090599</v>
@@ -2809,7 +2809,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="n">
         <v>0.067007</v>
       </c>
@@ -3342,7 +3346,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -3373,7 +3377,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>0.019428</v>
       </c>
@@ -4070,7 +4078,11 @@
           <t>Return of reclamation deposit</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -6505,7 +6517,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">

--- a/output/pdf_financials_xlsx/GTCH.xlsx
+++ b/output/pdf_financials_xlsx/GTCH.xlsx
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>1.932595</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>1.448973</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>0.79155</v>
       </c>
     </row>
     <row r="121">
@@ -4173,7 +4173,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>1.932595</v>
       </c>

--- a/output/pdf_financials_xlsx/GTCH.xlsx
+++ b/output/pdf_financials_xlsx/GTCH.xlsx
@@ -532,10 +532,10 @@
         <v>0.184811</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.16855</v>
+        <v>0.20755</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.145187</v>
+        <v>0.230437</v>
       </c>
     </row>
     <row r="8">
@@ -676,10 +676,10 @@
         <v>-7.009764</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-6.007177</v>
+        <v>-5.894563</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-3.126958</v>
+        <v>-3.068672</v>
       </c>
     </row>
     <row r="17">
@@ -692,10 +692,10 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.112614</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.058286</v>
       </c>
     </row>
     <row r="18">
@@ -864,10 +864,10 @@
         <v>-7.009764</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.007177</v>
+        <v>-5.894563</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.167091</v>
+        <v>-3.108805</v>
       </c>
     </row>
     <row r="28">
@@ -896,10 +896,10 @@
         <v>-6.997644</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.993502</v>
+        <v>-5.880888</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.143007</v>
+        <v>-3.084721</v>
       </c>
     </row>
     <row r="30">
@@ -934,10 +934,10 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.910472413306975</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.899388399933261</v>
       </c>
     </row>
     <row r="32">
@@ -2198,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.056846</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.38877</v>
       </c>
     </row>
     <row r="111">
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.017265</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -2588,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.017265</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         <v>-5.313881</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-4.035949</v>
+        <v>-4.053214</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-1.752973</v>
@@ -3660,7 +3660,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -3689,7 +3693,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -4047,7 +4055,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -6097,7 +6109,11 @@
           <t>Directors’ fees (Note 5)</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -6614,7 +6630,11 @@
           <t>Deferred income tax recovery (Note 7)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -6827,7 +6847,11 @@
           <t>DEFERRED INCOME TAX RECOVERY (Note 7)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
